--- a/docs/templates/Supplier_Inventory_Template_V1_CN.xlsx
+++ b/docs/templates/Supplier_Inventory_Template_V1_CN.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22300" windowHeight="11600"/>
+    <workbookView windowWidth="27660" windowHeight="11600"/>
   </bookViews>
   <sheets>
     <sheet name="供应商填写" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="135">
   <si>
     <t>供应商名称</t>
   </si>
@@ -79,6 +79,9 @@
     <t>口味明细</t>
   </si>
   <si>
+    <t>库存日期</t>
+  </si>
+  <si>
     <t>库存备注</t>
   </si>
   <si>
@@ -97,627 +100,271 @@
     <t>图片备注</t>
   </si>
   <si>
-    <t>X PRO VAPE</t>
-  </si>
-  <si>
-    <t>MARK</t>
-  </si>
-  <si>
-    <t>whatsapp / +86 15899880706</t>
-  </si>
-  <si>
-    <t>K 6000</t>
+    <t>【必填】供应商公司名称</t>
+  </si>
+  <si>
+    <t>【选填】主要联系人</t>
+  </si>
+  <si>
+    <t>【选填】WhatsApp / Telegram / 微信 / 邮箱</t>
+  </si>
+  <si>
+    <t>【必填】只填品牌，不要把型号写在这里</t>
+  </si>
+  <si>
+    <t>【必填】主要型号名称</t>
+  </si>
+  <si>
+    <t>【必填】Disposable / Pod System / Kit / E-liquid / Accessory</t>
+  </si>
+  <si>
+    <t>【推荐】只填数字</t>
+  </si>
+  <si>
+    <t>【必填】当前可售总量</t>
+  </si>
+  <si>
+    <t>【推荐】最小起订量</t>
+  </si>
+  <si>
+    <t>【必填】主要目标区域</t>
+  </si>
+  <si>
+    <t>【必填】城市, 国家/地区</t>
+  </si>
+  <si>
+    <t>【推荐】如有则填数字</t>
+  </si>
+  <si>
+    <t>【推荐】例如 5% 或 50mg</t>
+  </si>
+  <si>
+    <t>【推荐】例如 18ml</t>
+  </si>
+  <si>
+    <t>【推荐】用逗号分隔的口味概览</t>
+  </si>
+  <si>
+    <t>【选填】每个口味对应数量，可多行</t>
+  </si>
+  <si>
+    <t>【推荐】原始库存 / 发货 / 清仓备注</t>
+  </si>
+  <si>
+    <t>【选填】盒装 / 箱装信息</t>
+  </si>
+  <si>
+    <t>【选填】其他补充说明</t>
+  </si>
+  <si>
+    <t>【推荐】excel / chat / drive / url / zip</t>
+  </si>
+  <si>
+    <t>【推荐】文件名、链接、文件夹名或聊天引用</t>
+  </si>
+  <si>
+    <t>【选填】图片状况或来源说明</t>
+  </si>
+  <si>
+    <t>行 ID</t>
+  </si>
+  <si>
+    <t>准入分级</t>
+  </si>
+  <si>
+    <t>缺失字段</t>
+  </si>
+  <si>
+    <t>风险标记</t>
+  </si>
+  <si>
+    <t>人工复核重点</t>
+  </si>
+  <si>
+    <t>可转 Draft</t>
+  </si>
+  <si>
+    <t>原始图片状态</t>
+  </si>
+  <si>
+    <t>图片处理状态</t>
+  </si>
+  <si>
+    <t>可发布</t>
+  </si>
+  <si>
+    <t>审核备注</t>
+  </si>
+  <si>
+    <t>对应 Excel 行号或内部编号</t>
+  </si>
+  <si>
+    <t>从 Supplier_Input 复制</t>
+  </si>
+  <si>
+    <t>Green / Yellow / Red</t>
+  </si>
+  <si>
+    <t>列出关键缺失项</t>
+  </si>
+  <si>
+    <t>关键风险说明</t>
+  </si>
+  <si>
+    <t>优先检查什么</t>
+  </si>
+  <si>
+    <t>Yes / No</t>
+  </si>
+  <si>
+    <t>missing / received / extracted</t>
+  </si>
+  <si>
+    <t>raw_only / need_optimize / ready_for_upload / uploaded</t>
+  </si>
+  <si>
+    <t>仅内部使用</t>
+  </si>
+  <si>
+    <t>工作表</t>
+  </si>
+  <si>
+    <t>字段</t>
+  </si>
+  <si>
+    <t>级别</t>
+  </si>
+  <si>
+    <t>用途</t>
+  </si>
+  <si>
+    <t>示例</t>
+  </si>
+  <si>
+    <t>填写说明</t>
+  </si>
+  <si>
+    <t>Supplier_Input</t>
+  </si>
+  <si>
+    <t>必填</t>
+  </si>
+  <si>
+    <t>识别资料来源</t>
+  </si>
+  <si>
+    <t>深圳 ABC Trading</t>
+  </si>
+  <si>
+    <t>填写公司名称。</t>
+  </si>
+  <si>
+    <t>品牌识别</t>
+  </si>
+  <si>
+    <t>Vozol</t>
+  </si>
+  <si>
+    <t>只写品牌，不要混入型号。</t>
+  </si>
+  <si>
+    <t>主体型号</t>
+  </si>
+  <si>
+    <t>Star 10000</t>
+  </si>
+  <si>
+    <t>填写主要产品名。</t>
+  </si>
+  <si>
+    <t>类型归类</t>
   </si>
   <si>
     <t>Disposable</t>
   </si>
   <si>
+    <t>尽量使用下拉值。</t>
+  </si>
+  <si>
+    <t>推荐</t>
+  </si>
+  <si>
+    <t>交易单价</t>
+  </si>
+  <si>
     <t>3.20</t>
   </si>
   <si>
+    <t>只填数字，不要带币种文本。</t>
+  </si>
+  <si>
+    <t>当前库存量</t>
+  </si>
+  <si>
     <t>5000</t>
   </si>
   <si>
+    <t>尽量使用数字。</t>
+  </si>
+  <si>
+    <t>最小起订量</t>
+  </si>
+  <si>
     <t>500</t>
   </si>
   <si>
+    <t>主目标区域</t>
+  </si>
+  <si>
     <t>Middle East</t>
   </si>
   <si>
-    <t>shenzhen</t>
-  </si>
-  <si>
-    <t>5%</t>
-  </si>
-  <si>
-    <t>18ml</t>
-  </si>
-  <si>
-    <t>草莓西瓜～100
-桃子冰～100
-香蕉冰～200
-双苹果～100
-葡萄冰～200
-芒果冰～100
-百香果荔枝～100
-草莓猕猴桃～100
-菠萝猕猴桃～190
-石榴猕猴桃～100
-彩虹糖～3990
-芬达汽水～3860
-蓝莓薄荷～4070
-柠檬青柠～4050
-蓝莓冰纳～4070</t>
-  </si>
-  <si>
-    <r>
-      <t>草莓西瓜～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">100
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>桃子冰～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">100
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>香蕉冰～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">200
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>双苹果～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">100
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>葡萄冰～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">200
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>芒果冰～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">100
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>百香果荔枝～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">100
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>草莓猕猴桃～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">100
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>菠萝猕猴桃～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">190
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>石榴猕猴桃～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">100
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>彩虹糖～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">3990
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>芬达汽水～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">3860
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>蓝莓薄荷～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">4070
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>柠檬青柠～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">4050
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>蓝莓冰纳～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4070</t>
-    </r>
-  </si>
-  <si>
-    <t>库存正常</t>
-  </si>
-  <si>
-    <t>10 pcs/box, 200 pcs/carton</t>
+    <t>优先使用区域口径。</t>
+  </si>
+  <si>
+    <t>库存位置</t>
+  </si>
+  <si>
+    <t>Dubai, UAE</t>
+  </si>
+  <si>
+    <t>优先使用 城市, 国家/地区。</t>
+  </si>
+  <si>
+    <t>口味概览</t>
+  </si>
+  <si>
+    <t>Blue Razz Ice, Mint</t>
+  </si>
+  <si>
+    <t>使用逗号分隔。</t>
+  </si>
+  <si>
+    <t>选填</t>
+  </si>
+  <si>
+    <t>口味加数量</t>
+  </si>
+  <si>
+    <t>Blue Razz Ice - 300 pcs</t>
+  </si>
+  <si>
+    <t>有则每行一个口味。</t>
+  </si>
+  <si>
+    <t>原始库存上下文</t>
+  </si>
+  <si>
+    <t>Ready stock, sealed carton</t>
+  </si>
+  <si>
+    <t>允许原始运营备注。</t>
+  </si>
+  <si>
+    <t>图片从哪里来</t>
   </si>
   <si>
     <t>excel</t>
-  </si>
-  <si>
-    <t>VIHO</t>
-  </si>
-  <si>
-    <t>mark</t>
-  </si>
-  <si>
-    <t>VIHO vape</t>
-  </si>
-  <si>
-    <t>viho 20000</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>工厂</t>
-  </si>
-  <si>
-    <t>20ML</t>
-  </si>
-  <si>
-    <t>BLUEBERRY ICE  28748
-SOUR APPLE ICE  20923
-BLUEBERRY POM  1734
-CRISP APPLE BERRY  4
-KIWI STRAWBERRY 36
-LEMON PIE  29</t>
-  </si>
-  <si>
-    <t>库存正常，没有喷码</t>
-  </si>
-  <si>
-    <t>【必填】供应商公司名称</t>
-  </si>
-  <si>
-    <t>【选填】主要联系人</t>
-  </si>
-  <si>
-    <t>【选填】WhatsApp / Telegram / 微信 / 邮箱</t>
-  </si>
-  <si>
-    <t>【必填】只填品牌，不要把型号写在这里</t>
-  </si>
-  <si>
-    <t>【必填】主要型号名称</t>
-  </si>
-  <si>
-    <t>【必填】Disposable / Pod System / Kit / E-liquid / Accessory</t>
-  </si>
-  <si>
-    <t>【推荐】只填数字</t>
-  </si>
-  <si>
-    <t>【必填】当前可售总量</t>
-  </si>
-  <si>
-    <t>【推荐】最小起订量</t>
-  </si>
-  <si>
-    <t>【必填】主要目标区域</t>
-  </si>
-  <si>
-    <t>【必填】城市, 国家/地区</t>
-  </si>
-  <si>
-    <t>【推荐】如有则填数字</t>
-  </si>
-  <si>
-    <t>【推荐】例如 5% 或 50mg</t>
-  </si>
-  <si>
-    <t>【推荐】例如 18ml</t>
-  </si>
-  <si>
-    <t>【推荐】用逗号分隔的口味概览</t>
-  </si>
-  <si>
-    <t>【选填】每个口味对应数量，可多行</t>
-  </si>
-  <si>
-    <t>【推荐】原始库存 / 发货 / 清仓备注</t>
-  </si>
-  <si>
-    <t>【选填】盒装 / 箱装信息</t>
-  </si>
-  <si>
-    <t>【选填】其他补充说明</t>
-  </si>
-  <si>
-    <t>【推荐】excel / chat / drive / url / zip</t>
-  </si>
-  <si>
-    <t>【推荐】文件名、链接、文件夹名或聊天引用</t>
-  </si>
-  <si>
-    <t>【选填】图片状况或来源说明</t>
-  </si>
-  <si>
-    <t>行 ID</t>
-  </si>
-  <si>
-    <t>准入分级</t>
-  </si>
-  <si>
-    <t>缺失字段</t>
-  </si>
-  <si>
-    <t>风险标记</t>
-  </si>
-  <si>
-    <t>人工复核重点</t>
-  </si>
-  <si>
-    <t>可转 Draft</t>
-  </si>
-  <si>
-    <t>原始图片状态</t>
-  </si>
-  <si>
-    <t>图片处理状态</t>
-  </si>
-  <si>
-    <t>可发布</t>
-  </si>
-  <si>
-    <t>审核备注</t>
-  </si>
-  <si>
-    <t>对应 Excel 行号或内部编号</t>
-  </si>
-  <si>
-    <t>从 Supplier_Input 复制</t>
-  </si>
-  <si>
-    <t>Green / Yellow / Red</t>
-  </si>
-  <si>
-    <t>列出关键缺失项</t>
-  </si>
-  <si>
-    <t>关键风险说明</t>
-  </si>
-  <si>
-    <t>优先检查什么</t>
-  </si>
-  <si>
-    <t>Yes / No</t>
-  </si>
-  <si>
-    <t>missing / received / extracted</t>
-  </si>
-  <si>
-    <t>raw_only / need_optimize / ready_for_upload / uploaded</t>
-  </si>
-  <si>
-    <t>仅内部使用</t>
-  </si>
-  <si>
-    <t>工作表</t>
-  </si>
-  <si>
-    <t>字段</t>
-  </si>
-  <si>
-    <t>级别</t>
-  </si>
-  <si>
-    <t>用途</t>
-  </si>
-  <si>
-    <t>示例</t>
-  </si>
-  <si>
-    <t>填写说明</t>
-  </si>
-  <si>
-    <t>Supplier_Input</t>
-  </si>
-  <si>
-    <t>必填</t>
-  </si>
-  <si>
-    <t>识别资料来源</t>
-  </si>
-  <si>
-    <t>深圳 ABC Trading</t>
-  </si>
-  <si>
-    <t>填写公司名称。</t>
-  </si>
-  <si>
-    <t>品牌识别</t>
-  </si>
-  <si>
-    <t>Vozol</t>
-  </si>
-  <si>
-    <t>只写品牌，不要混入型号。</t>
-  </si>
-  <si>
-    <t>主体型号</t>
-  </si>
-  <si>
-    <t>Star 10000</t>
-  </si>
-  <si>
-    <t>填写主要产品名。</t>
-  </si>
-  <si>
-    <t>类型归类</t>
-  </si>
-  <si>
-    <t>尽量使用下拉值。</t>
-  </si>
-  <si>
-    <t>推荐</t>
-  </si>
-  <si>
-    <t>交易单价</t>
-  </si>
-  <si>
-    <t>只填数字，不要带币种文本。</t>
-  </si>
-  <si>
-    <t>当前库存量</t>
-  </si>
-  <si>
-    <t>尽量使用数字。</t>
-  </si>
-  <si>
-    <t>最小起订量</t>
-  </si>
-  <si>
-    <t>主目标区域</t>
-  </si>
-  <si>
-    <t>优先使用区域口径。</t>
-  </si>
-  <si>
-    <t>库存位置</t>
-  </si>
-  <si>
-    <t>Dubai, UAE</t>
-  </si>
-  <si>
-    <t>优先使用 城市, 国家/地区。</t>
-  </si>
-  <si>
-    <t>口味概览</t>
-  </si>
-  <si>
-    <t>Blue Razz Ice, Mint</t>
-  </si>
-  <si>
-    <t>使用逗号分隔。</t>
-  </si>
-  <si>
-    <t>选填</t>
-  </si>
-  <si>
-    <t>口味加数量</t>
-  </si>
-  <si>
-    <t>Blue Razz Ice - 300 pcs</t>
-  </si>
-  <si>
-    <t>有则每行一个口味。</t>
-  </si>
-  <si>
-    <t>原始库存上下文</t>
-  </si>
-  <si>
-    <t>Ready stock, sealed carton</t>
-  </si>
-  <si>
-    <t>允许原始运营备注。</t>
-  </si>
-  <si>
-    <t>图片从哪里来</t>
   </si>
   <si>
     <t>使用 excel/chat/drive/url/zip。</t>
@@ -799,7 +446,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -828,24 +475,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="10"/>
-      <color rgb="FF666666"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体-简"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体-简"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -992,7 +626,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1019,7 +653,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1346,19 +986,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1367,131 +1016,122 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1505,29 +1145,21 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1875,7 +1507,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V105"/>
+  <dimension ref="A1:W103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1891,15 +1523,15 @@
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="14" width="16" customWidth="1"/>
     <col min="15" max="15" width="28" customWidth="1"/>
-    <col min="16" max="16" width="32" customWidth="1"/>
-    <col min="17" max="17" width="36" customWidth="1"/>
-    <col min="18" max="19" width="24" customWidth="1"/>
-    <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="28" customWidth="1"/>
-    <col min="22" max="22" width="26" customWidth="1"/>
+    <col min="16" max="17" width="32" customWidth="1"/>
+    <col min="18" max="18" width="36" customWidth="1"/>
+    <col min="19" max="20" width="24" customWidth="1"/>
+    <col min="21" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="28" customWidth="1"/>
+    <col min="23" max="23" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:22">
+    <row r="1" ht="24" customHeight="1" spans="1:23">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1948,7 +1580,7 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="10" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="3" t="s">
@@ -1966,224 +1598,155 @@
       <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" ht="145" customHeight="1" spans="1:22">
-      <c r="A2" s="5" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="5" t="s">
+    </row>
+    <row r="2" s="5" customFormat="1" ht="24" customHeight="1" spans="1:23">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+    </row>
+    <row r="3" s="6" customFormat="1" ht="69" customHeight="1" spans="1:23">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="C3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="D3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="E3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="F3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="G3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="H3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="I3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="5">
-        <v>6000</v>
-      </c>
-      <c r="M2" s="5" t="s">
+      <c r="J3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="K3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="N3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="O3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5" t="s">
+      <c r="P3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-    </row>
-    <row r="3" ht="244" customHeight="1" spans="1:22">
-      <c r="A3" s="6" t="s">
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="S3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="T3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="U3" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="7">
-        <v>3</v>
-      </c>
-      <c r="H3" s="6">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="7">
-        <v>500</v>
-      </c>
-      <c r="J3" s="6" t="s">
+      <c r="V3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="W3" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="7">
-        <v>10000</v>
-      </c>
-      <c r="M3" s="10">
-        <v>0.05</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q3" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S3" s="7"/>
-      <c r="T3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-    </row>
-    <row r="4" ht="69" customHeight="1" spans="1:22">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-    </row>
-    <row r="5" ht="69" customHeight="1" spans="1:22">
-      <c r="A5" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="V5" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+    </row>
+    <row r="6" spans="1:23">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2206,8 +1769,9 @@
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="W6" s="2"/>
+    </row>
+    <row r="7" spans="1:23">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -2230,8 +1794,9 @@
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="W7" s="2"/>
+    </row>
+    <row r="8" spans="1:23">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2254,8 +1819,9 @@
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="W8" s="2"/>
+    </row>
+    <row r="9" spans="1:23">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -2278,8 +1844,9 @@
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="W9" s="2"/>
+    </row>
+    <row r="10" spans="1:23">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -2302,8 +1869,9 @@
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="W10" s="2"/>
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2326,8 +1894,9 @@
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="W11" s="2"/>
+    </row>
+    <row r="12" spans="1:23">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2350,8 +1919,9 @@
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="W12" s="2"/>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2374,8 +1944,9 @@
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="W13" s="2"/>
+    </row>
+    <row r="14" spans="1:23">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -2398,8 +1969,9 @@
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="W14" s="2"/>
+    </row>
+    <row r="15" spans="1:23">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2422,8 +1994,9 @@
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="W15" s="2"/>
+    </row>
+    <row r="16" spans="1:23">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2446,8 +2019,9 @@
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="W16" s="2"/>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2470,8 +2044,9 @@
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="W17" s="2"/>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2494,8 +2069,9 @@
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="W18" s="2"/>
+    </row>
+    <row r="19" spans="1:23">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2518,8 +2094,9 @@
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="W19" s="2"/>
+    </row>
+    <row r="20" spans="1:23">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2542,8 +2119,9 @@
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="W20" s="2"/>
+    </row>
+    <row r="21" spans="1:23">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2566,8 +2144,9 @@
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="W21" s="2"/>
+    </row>
+    <row r="22" spans="1:23">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2590,8 +2169,9 @@
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
       <c r="V22" s="2"/>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="W22" s="2"/>
+    </row>
+    <row r="23" spans="1:23">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2614,8 +2194,9 @@
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="W23" s="2"/>
+    </row>
+    <row r="24" spans="1:23">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2638,8 +2219,9 @@
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="W24" s="2"/>
+    </row>
+    <row r="25" spans="1:23">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2662,8 +2244,9 @@
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
-    </row>
-    <row r="26" spans="1:22">
+      <c r="W25" s="2"/>
+    </row>
+    <row r="26" spans="1:23">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2686,8 +2269,9 @@
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
-    </row>
-    <row r="27" spans="1:22">
+      <c r="W26" s="2"/>
+    </row>
+    <row r="27" spans="1:23">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2710,8 +2294,9 @@
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
-    </row>
-    <row r="28" spans="1:22">
+      <c r="W27" s="2"/>
+    </row>
+    <row r="28" spans="1:23">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2734,8 +2319,9 @@
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
-    </row>
-    <row r="29" spans="1:22">
+      <c r="W28" s="2"/>
+    </row>
+    <row r="29" spans="1:23">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -2758,8 +2344,9 @@
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
-    </row>
-    <row r="30" spans="1:22">
+      <c r="W29" s="2"/>
+    </row>
+    <row r="30" spans="1:23">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2782,8 +2369,9 @@
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
       <c r="V30" s="2"/>
-    </row>
-    <row r="31" spans="1:22">
+      <c r="W30" s="2"/>
+    </row>
+    <row r="31" spans="1:23">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2806,8 +2394,9 @@
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
-    </row>
-    <row r="32" spans="1:22">
+      <c r="W31" s="2"/>
+    </row>
+    <row r="32" spans="1:23">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2830,8 +2419,9 @@
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="W32" s="2"/>
+    </row>
+    <row r="33" spans="1:23">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2854,8 +2444,9 @@
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
       <c r="V33" s="2"/>
-    </row>
-    <row r="34" spans="1:22">
+      <c r="W33" s="2"/>
+    </row>
+    <row r="34" spans="1:23">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2878,8 +2469,9 @@
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
       <c r="V34" s="2"/>
-    </row>
-    <row r="35" spans="1:22">
+      <c r="W34" s="2"/>
+    </row>
+    <row r="35" spans="1:23">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2902,8 +2494,9 @@
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
       <c r="V35" s="2"/>
-    </row>
-    <row r="36" spans="1:22">
+      <c r="W35" s="2"/>
+    </row>
+    <row r="36" spans="1:23">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2926,8 +2519,9 @@
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
       <c r="V36" s="2"/>
-    </row>
-    <row r="37" spans="1:22">
+      <c r="W36" s="2"/>
+    </row>
+    <row r="37" spans="1:23">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2950,8 +2544,9 @@
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
       <c r="V37" s="2"/>
-    </row>
-    <row r="38" spans="1:22">
+      <c r="W37" s="2"/>
+    </row>
+    <row r="38" spans="1:23">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2974,8 +2569,9 @@
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
-    </row>
-    <row r="39" spans="1:22">
+      <c r="W38" s="2"/>
+    </row>
+    <row r="39" spans="1:23">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2998,8 +2594,9 @@
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
       <c r="V39" s="2"/>
-    </row>
-    <row r="40" spans="1:22">
+      <c r="W39" s="2"/>
+    </row>
+    <row r="40" spans="1:23">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -3022,8 +2619,9 @@
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
       <c r="V40" s="2"/>
-    </row>
-    <row r="41" spans="1:22">
+      <c r="W40" s="2"/>
+    </row>
+    <row r="41" spans="1:23">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -3046,8 +2644,9 @@
       <c r="T41" s="2"/>
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
-    </row>
-    <row r="42" spans="1:22">
+      <c r="W41" s="2"/>
+    </row>
+    <row r="42" spans="1:23">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -3070,8 +2669,9 @@
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
       <c r="V42" s="2"/>
-    </row>
-    <row r="43" spans="1:22">
+      <c r="W42" s="2"/>
+    </row>
+    <row r="43" spans="1:23">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -3094,8 +2694,9 @@
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
       <c r="V43" s="2"/>
-    </row>
-    <row r="44" spans="1:22">
+      <c r="W43" s="2"/>
+    </row>
+    <row r="44" spans="1:23">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -3118,8 +2719,9 @@
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
-    </row>
-    <row r="45" spans="1:22">
+      <c r="W44" s="2"/>
+    </row>
+    <row r="45" spans="1:23">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -3142,8 +2744,9 @@
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
-    </row>
-    <row r="46" spans="1:22">
+      <c r="W45" s="2"/>
+    </row>
+    <row r="46" spans="1:23">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -3166,8 +2769,9 @@
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
       <c r="V46" s="2"/>
-    </row>
-    <row r="47" spans="1:22">
+      <c r="W46" s="2"/>
+    </row>
+    <row r="47" spans="1:23">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -3190,8 +2794,9 @@
       <c r="T47" s="2"/>
       <c r="U47" s="2"/>
       <c r="V47" s="2"/>
-    </row>
-    <row r="48" spans="1:22">
+      <c r="W47" s="2"/>
+    </row>
+    <row r="48" spans="1:23">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3214,8 +2819,9 @@
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
       <c r="V48" s="2"/>
-    </row>
-    <row r="49" spans="1:22">
+      <c r="W48" s="2"/>
+    </row>
+    <row r="49" spans="1:23">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -3238,8 +2844,9 @@
       <c r="T49" s="2"/>
       <c r="U49" s="2"/>
       <c r="V49" s="2"/>
-    </row>
-    <row r="50" spans="1:22">
+      <c r="W49" s="2"/>
+    </row>
+    <row r="50" spans="1:23">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3262,8 +2869,9 @@
       <c r="T50" s="2"/>
       <c r="U50" s="2"/>
       <c r="V50" s="2"/>
-    </row>
-    <row r="51" spans="1:22">
+      <c r="W50" s="2"/>
+    </row>
+    <row r="51" spans="1:23">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -3286,8 +2894,9 @@
       <c r="T51" s="2"/>
       <c r="U51" s="2"/>
       <c r="V51" s="2"/>
-    </row>
-    <row r="52" spans="1:22">
+      <c r="W51" s="2"/>
+    </row>
+    <row r="52" spans="1:23">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -3310,8 +2919,9 @@
       <c r="T52" s="2"/>
       <c r="U52" s="2"/>
       <c r="V52" s="2"/>
-    </row>
-    <row r="53" spans="1:22">
+      <c r="W52" s="2"/>
+    </row>
+    <row r="53" spans="1:23">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -3334,8 +2944,9 @@
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
       <c r="V53" s="2"/>
-    </row>
-    <row r="54" spans="1:22">
+      <c r="W53" s="2"/>
+    </row>
+    <row r="54" spans="1:23">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -3358,8 +2969,9 @@
       <c r="T54" s="2"/>
       <c r="U54" s="2"/>
       <c r="V54" s="2"/>
-    </row>
-    <row r="55" spans="1:22">
+      <c r="W54" s="2"/>
+    </row>
+    <row r="55" spans="1:23">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -3382,8 +2994,9 @@
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
       <c r="V55" s="2"/>
-    </row>
-    <row r="56" spans="1:22">
+      <c r="W55" s="2"/>
+    </row>
+    <row r="56" spans="1:23">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -3406,8 +3019,9 @@
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
       <c r="V56" s="2"/>
-    </row>
-    <row r="57" spans="1:22">
+      <c r="W56" s="2"/>
+    </row>
+    <row r="57" spans="1:23">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -3430,8 +3044,9 @@
       <c r="T57" s="2"/>
       <c r="U57" s="2"/>
       <c r="V57" s="2"/>
-    </row>
-    <row r="58" spans="1:22">
+      <c r="W57" s="2"/>
+    </row>
+    <row r="58" spans="1:23">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -3454,8 +3069,9 @@
       <c r="T58" s="2"/>
       <c r="U58" s="2"/>
       <c r="V58" s="2"/>
-    </row>
-    <row r="59" spans="1:22">
+      <c r="W58" s="2"/>
+    </row>
+    <row r="59" spans="1:23">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -3478,8 +3094,9 @@
       <c r="T59" s="2"/>
       <c r="U59" s="2"/>
       <c r="V59" s="2"/>
-    </row>
-    <row r="60" spans="1:22">
+      <c r="W59" s="2"/>
+    </row>
+    <row r="60" spans="1:23">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -3502,8 +3119,9 @@
       <c r="T60" s="2"/>
       <c r="U60" s="2"/>
       <c r="V60" s="2"/>
-    </row>
-    <row r="61" spans="1:22">
+      <c r="W60" s="2"/>
+    </row>
+    <row r="61" spans="1:23">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3526,8 +3144,9 @@
       <c r="T61" s="2"/>
       <c r="U61" s="2"/>
       <c r="V61" s="2"/>
-    </row>
-    <row r="62" spans="1:22">
+      <c r="W61" s="2"/>
+    </row>
+    <row r="62" spans="1:23">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -3550,8 +3169,9 @@
       <c r="T62" s="2"/>
       <c r="U62" s="2"/>
       <c r="V62" s="2"/>
-    </row>
-    <row r="63" spans="1:22">
+      <c r="W62" s="2"/>
+    </row>
+    <row r="63" spans="1:23">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3574,8 +3194,9 @@
       <c r="T63" s="2"/>
       <c r="U63" s="2"/>
       <c r="V63" s="2"/>
-    </row>
-    <row r="64" spans="1:22">
+      <c r="W63" s="2"/>
+    </row>
+    <row r="64" spans="1:23">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3598,8 +3219,9 @@
       <c r="T64" s="2"/>
       <c r="U64" s="2"/>
       <c r="V64" s="2"/>
-    </row>
-    <row r="65" spans="1:22">
+      <c r="W64" s="2"/>
+    </row>
+    <row r="65" spans="1:23">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -3622,8 +3244,9 @@
       <c r="T65" s="2"/>
       <c r="U65" s="2"/>
       <c r="V65" s="2"/>
-    </row>
-    <row r="66" spans="1:22">
+      <c r="W65" s="2"/>
+    </row>
+    <row r="66" spans="1:23">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -3646,8 +3269,9 @@
       <c r="T66" s="2"/>
       <c r="U66" s="2"/>
       <c r="V66" s="2"/>
-    </row>
-    <row r="67" spans="1:22">
+      <c r="W66" s="2"/>
+    </row>
+    <row r="67" spans="1:23">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3670,8 +3294,9 @@
       <c r="T67" s="2"/>
       <c r="U67" s="2"/>
       <c r="V67" s="2"/>
-    </row>
-    <row r="68" spans="1:22">
+      <c r="W67" s="2"/>
+    </row>
+    <row r="68" spans="1:23">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -3694,8 +3319,9 @@
       <c r="T68" s="2"/>
       <c r="U68" s="2"/>
       <c r="V68" s="2"/>
-    </row>
-    <row r="69" spans="1:22">
+      <c r="W68" s="2"/>
+    </row>
+    <row r="69" spans="1:23">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3718,8 +3344,9 @@
       <c r="T69" s="2"/>
       <c r="U69" s="2"/>
       <c r="V69" s="2"/>
-    </row>
-    <row r="70" spans="1:22">
+      <c r="W69" s="2"/>
+    </row>
+    <row r="70" spans="1:23">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -3742,8 +3369,9 @@
       <c r="T70" s="2"/>
       <c r="U70" s="2"/>
       <c r="V70" s="2"/>
-    </row>
-    <row r="71" spans="1:22">
+      <c r="W70" s="2"/>
+    </row>
+    <row r="71" spans="1:23">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3766,8 +3394,9 @@
       <c r="T71" s="2"/>
       <c r="U71" s="2"/>
       <c r="V71" s="2"/>
-    </row>
-    <row r="72" spans="1:22">
+      <c r="W71" s="2"/>
+    </row>
+    <row r="72" spans="1:23">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3790,8 +3419,9 @@
       <c r="T72" s="2"/>
       <c r="U72" s="2"/>
       <c r="V72" s="2"/>
-    </row>
-    <row r="73" spans="1:22">
+      <c r="W72" s="2"/>
+    </row>
+    <row r="73" spans="1:23">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -3814,8 +3444,9 @@
       <c r="T73" s="2"/>
       <c r="U73" s="2"/>
       <c r="V73" s="2"/>
-    </row>
-    <row r="74" spans="1:22">
+      <c r="W73" s="2"/>
+    </row>
+    <row r="74" spans="1:23">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -3838,8 +3469,9 @@
       <c r="T74" s="2"/>
       <c r="U74" s="2"/>
       <c r="V74" s="2"/>
-    </row>
-    <row r="75" spans="1:22">
+      <c r="W74" s="2"/>
+    </row>
+    <row r="75" spans="1:23">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -3862,8 +3494,9 @@
       <c r="T75" s="2"/>
       <c r="U75" s="2"/>
       <c r="V75" s="2"/>
-    </row>
-    <row r="76" spans="1:22">
+      <c r="W75" s="2"/>
+    </row>
+    <row r="76" spans="1:23">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -3886,8 +3519,9 @@
       <c r="T76" s="2"/>
       <c r="U76" s="2"/>
       <c r="V76" s="2"/>
-    </row>
-    <row r="77" spans="1:22">
+      <c r="W76" s="2"/>
+    </row>
+    <row r="77" spans="1:23">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -3910,8 +3544,9 @@
       <c r="T77" s="2"/>
       <c r="U77" s="2"/>
       <c r="V77" s="2"/>
-    </row>
-    <row r="78" spans="1:22">
+      <c r="W77" s="2"/>
+    </row>
+    <row r="78" spans="1:23">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -3934,8 +3569,9 @@
       <c r="T78" s="2"/>
       <c r="U78" s="2"/>
       <c r="V78" s="2"/>
-    </row>
-    <row r="79" spans="1:22">
+      <c r="W78" s="2"/>
+    </row>
+    <row r="79" spans="1:23">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -3958,8 +3594,9 @@
       <c r="T79" s="2"/>
       <c r="U79" s="2"/>
       <c r="V79" s="2"/>
-    </row>
-    <row r="80" spans="1:22">
+      <c r="W79" s="2"/>
+    </row>
+    <row r="80" spans="1:23">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -3982,8 +3619,9 @@
       <c r="T80" s="2"/>
       <c r="U80" s="2"/>
       <c r="V80" s="2"/>
-    </row>
-    <row r="81" spans="1:22">
+      <c r="W80" s="2"/>
+    </row>
+    <row r="81" spans="1:23">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -4006,8 +3644,9 @@
       <c r="T81" s="2"/>
       <c r="U81" s="2"/>
       <c r="V81" s="2"/>
-    </row>
-    <row r="82" spans="1:22">
+      <c r="W81" s="2"/>
+    </row>
+    <row r="82" spans="1:23">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -4030,8 +3669,9 @@
       <c r="T82" s="2"/>
       <c r="U82" s="2"/>
       <c r="V82" s="2"/>
-    </row>
-    <row r="83" spans="1:22">
+      <c r="W82" s="2"/>
+    </row>
+    <row r="83" spans="1:23">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -4054,8 +3694,9 @@
       <c r="T83" s="2"/>
       <c r="U83" s="2"/>
       <c r="V83" s="2"/>
-    </row>
-    <row r="84" spans="1:22">
+      <c r="W83" s="2"/>
+    </row>
+    <row r="84" spans="1:23">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -4078,8 +3719,9 @@
       <c r="T84" s="2"/>
       <c r="U84" s="2"/>
       <c r="V84" s="2"/>
-    </row>
-    <row r="85" spans="1:22">
+      <c r="W84" s="2"/>
+    </row>
+    <row r="85" spans="1:23">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -4102,8 +3744,9 @@
       <c r="T85" s="2"/>
       <c r="U85" s="2"/>
       <c r="V85" s="2"/>
-    </row>
-    <row r="86" spans="1:22">
+      <c r="W85" s="2"/>
+    </row>
+    <row r="86" spans="1:23">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -4126,8 +3769,9 @@
       <c r="T86" s="2"/>
       <c r="U86" s="2"/>
       <c r="V86" s="2"/>
-    </row>
-    <row r="87" spans="1:22">
+      <c r="W86" s="2"/>
+    </row>
+    <row r="87" spans="1:23">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -4150,8 +3794,9 @@
       <c r="T87" s="2"/>
       <c r="U87" s="2"/>
       <c r="V87" s="2"/>
-    </row>
-    <row r="88" spans="1:22">
+      <c r="W87" s="2"/>
+    </row>
+    <row r="88" spans="1:23">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -4174,8 +3819,9 @@
       <c r="T88" s="2"/>
       <c r="U88" s="2"/>
       <c r="V88" s="2"/>
-    </row>
-    <row r="89" spans="1:22">
+      <c r="W88" s="2"/>
+    </row>
+    <row r="89" spans="1:23">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -4198,8 +3844,9 @@
       <c r="T89" s="2"/>
       <c r="U89" s="2"/>
       <c r="V89" s="2"/>
-    </row>
-    <row r="90" spans="1:22">
+      <c r="W89" s="2"/>
+    </row>
+    <row r="90" spans="1:23">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -4222,8 +3869,9 @@
       <c r="T90" s="2"/>
       <c r="U90" s="2"/>
       <c r="V90" s="2"/>
-    </row>
-    <row r="91" spans="1:22">
+      <c r="W90" s="2"/>
+    </row>
+    <row r="91" spans="1:23">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -4246,8 +3894,9 @@
       <c r="T91" s="2"/>
       <c r="U91" s="2"/>
       <c r="V91" s="2"/>
-    </row>
-    <row r="92" spans="1:22">
+      <c r="W91" s="2"/>
+    </row>
+    <row r="92" spans="1:23">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -4270,8 +3919,9 @@
       <c r="T92" s="2"/>
       <c r="U92" s="2"/>
       <c r="V92" s="2"/>
-    </row>
-    <row r="93" spans="1:22">
+      <c r="W92" s="2"/>
+    </row>
+    <row r="93" spans="1:23">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -4294,8 +3944,9 @@
       <c r="T93" s="2"/>
       <c r="U93" s="2"/>
       <c r="V93" s="2"/>
-    </row>
-    <row r="94" spans="1:22">
+      <c r="W93" s="2"/>
+    </row>
+    <row r="94" spans="1:23">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -4318,8 +3969,9 @@
       <c r="T94" s="2"/>
       <c r="U94" s="2"/>
       <c r="V94" s="2"/>
-    </row>
-    <row r="95" spans="1:22">
+      <c r="W94" s="2"/>
+    </row>
+    <row r="95" spans="1:23">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -4342,8 +3994,9 @@
       <c r="T95" s="2"/>
       <c r="U95" s="2"/>
       <c r="V95" s="2"/>
-    </row>
-    <row r="96" spans="1:22">
+      <c r="W95" s="2"/>
+    </row>
+    <row r="96" spans="1:23">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -4366,8 +4019,9 @@
       <c r="T96" s="2"/>
       <c r="U96" s="2"/>
       <c r="V96" s="2"/>
-    </row>
-    <row r="97" spans="1:22">
+      <c r="W96" s="2"/>
+    </row>
+    <row r="97" spans="1:23">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -4390,8 +4044,9 @@
       <c r="T97" s="2"/>
       <c r="U97" s="2"/>
       <c r="V97" s="2"/>
-    </row>
-    <row r="98" spans="1:22">
+      <c r="W97" s="2"/>
+    </row>
+    <row r="98" spans="1:23">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -4414,8 +4069,9 @@
       <c r="T98" s="2"/>
       <c r="U98" s="2"/>
       <c r="V98" s="2"/>
-    </row>
-    <row r="99" spans="1:22">
+      <c r="W98" s="2"/>
+    </row>
+    <row r="99" spans="1:23">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -4438,8 +4094,9 @@
       <c r="T99" s="2"/>
       <c r="U99" s="2"/>
       <c r="V99" s="2"/>
-    </row>
-    <row r="100" spans="1:22">
+      <c r="W99" s="2"/>
+    </row>
+    <row r="100" spans="1:23">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -4462,8 +4119,9 @@
       <c r="T100" s="2"/>
       <c r="U100" s="2"/>
       <c r="V100" s="2"/>
-    </row>
-    <row r="101" spans="1:22">
+      <c r="W100" s="2"/>
+    </row>
+    <row r="101" spans="1:23">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -4486,8 +4144,9 @@
       <c r="T101" s="2"/>
       <c r="U101" s="2"/>
       <c r="V101" s="2"/>
-    </row>
-    <row r="102" spans="1:22">
+      <c r="W101" s="2"/>
+    </row>
+    <row r="102" spans="1:23">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -4510,8 +4169,9 @@
       <c r="T102" s="2"/>
       <c r="U102" s="2"/>
       <c r="V102" s="2"/>
-    </row>
-    <row r="103" spans="1:22">
+      <c r="W102" s="2"/>
+    </row>
+    <row r="103" spans="1:23">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -4534,61 +4194,14 @@
       <c r="T103" s="2"/>
       <c r="U103" s="2"/>
       <c r="V103" s="2"/>
-    </row>
-    <row r="104" spans="1:22">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
-      <c r="L104" s="2"/>
-      <c r="M104" s="2"/>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
-      <c r="P104" s="2"/>
-      <c r="Q104" s="2"/>
-      <c r="R104" s="2"/>
-      <c r="S104" s="2"/>
-      <c r="T104" s="2"/>
-      <c r="U104" s="2"/>
-      <c r="V104" s="2"/>
-    </row>
-    <row r="105" spans="1:22">
-      <c r="A105" s="2"/>
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2"/>
-      <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
-      <c r="L105" s="2"/>
-      <c r="M105" s="2"/>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
-      <c r="P105" s="2"/>
-      <c r="Q105" s="2"/>
-      <c r="R105" s="2"/>
-      <c r="S105" s="2"/>
-      <c r="T105" s="2"/>
-      <c r="U105" s="2"/>
-      <c r="V105" s="2"/>
+      <c r="W103" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="F6:F106">
+    <dataValidation type="list" allowBlank="1" sqref="F4:F104">
       <formula1>"Disposable,Pod System,Kit,E-liquid,Accessory"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T6:T106">
+    <dataValidation type="list" allowBlank="1" sqref="U4:U104">
       <formula1>"excel,chat,drive,url,zip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4619,7 +4232,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:13">
       <c r="A1" s="3" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -4631,72 +4244,72 @@
         <v>4</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6234,422 +5847,422 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" ht="29" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" ht="29" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" ht="29" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
